--- a/results/soae_T_xi [int 100ms, bw=10p max, kaiser, df=50hz, rip=100db, crop=200hz, tau=500ms, hop_psd=250ms, nfft=None, win=hann].xlsx
+++ b/results/soae_T_xi [int 100ms, bw=10p max, kaiser, df=50hz, rip=100db, crop=200hz, tau=500ms, hop_psd=250ms, nfft=None, win=hann].xlsx
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.01517734560733591</v>
+        <v>0.01517299684036841</v>
       </c>
       <c r="F2" t="n">
         <v>10.09595355218707</v>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.01369010189923215</v>
+        <v>0.01369601306671181</v>
       </c>
       <c r="F3" t="n">
         <v>10.09595355218707</v>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05565287389668351</v>
+        <v>0.0556362703747408</v>
       </c>
       <c r="F4" t="n">
         <v>3.09945385050024</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.04858014616926393</v>
+        <v>0.04851914069705662</v>
       </c>
       <c r="F5" t="n">
         <v>3.09945385050024</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.09339812714812197</v>
+        <v>0.09340124039097339</v>
       </c>
       <c r="F6" t="n">
         <v>0.8253318426568844</v>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.09366998620976152</v>
+        <v>0.09368840625508595</v>
       </c>
       <c r="F7" t="n">
         <v>0.8253318426568844</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.07011988516958659</v>
+        <v>0.07015579445283308</v>
       </c>
       <c r="F8" t="n">
         <v>2.212581609474567</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.0669982316763255</v>
+        <v>0.0670288221670698</v>
       </c>
       <c r="F9" t="n">
         <v>2.212581609474567</v>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.05856465004178425</v>
+        <v>0.05857167314846416</v>
       </c>
       <c r="F10" t="n">
         <v>1.306834054289299</v>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.06247186349251897</v>
+        <v>0.06248967338965735</v>
       </c>
       <c r="F11" t="n">
         <v>1.306834054289299</v>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.09387110663095767</v>
+        <v>0.09387476423584565</v>
       </c>
       <c r="F12" t="n">
         <v>1.226981092761272</v>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.09445376392844394</v>
+        <v>0.09447175535587791</v>
       </c>
       <c r="F13" t="n">
         <v>1.226981092761272</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.05303948794804957</v>
+        <v>0.05303728341500252</v>
       </c>
       <c r="F14" t="n">
         <v>2.396894500224019</v>
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.04929461714265029</v>
+        <v>0.04925778549617359</v>
       </c>
       <c r="F15" t="n">
         <v>2.396894500224019</v>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.08891279194686193</v>
+        <v>0.08890171006703744</v>
       </c>
       <c r="F16" t="n">
         <v>1.618801456042487</v>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.08122644537754177</v>
+        <v>0.08122291981049649</v>
       </c>
       <c r="F17" t="n">
         <v>1.618801456042487</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.08145073616734519</v>
+        <v>0.08146016187351383</v>
       </c>
       <c r="F18" t="n">
         <v>0.8820415846920716</v>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.08495488676669596</v>
+        <v>0.08507551768898693</v>
       </c>
       <c r="F19" t="n">
         <v>0.8820415846920716</v>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.05655333285093746</v>
+        <v>0.05661062878666115</v>
       </c>
       <c r="F20" t="n">
         <v>2.415225068705968</v>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.05456603639583093</v>
+        <v>0.05459009815361449</v>
       </c>
       <c r="F21" t="n">
         <v>2.415225068705968</v>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.08616370212387135</v>
+        <v>0.08617559429018509</v>
       </c>
       <c r="F22" t="n">
         <v>1.281367686769816</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.08860394666234968</v>
+        <v>0.08862075707023429</v>
       </c>
       <c r="F23" t="n">
         <v>1.281367686769816</v>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.01429365255356686</v>
+        <v>0.01429595048703679</v>
       </c>
       <c r="F24" t="n">
         <v>10.05992016213009</v>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.01265826411806013</v>
+        <v>0.01266345831049105</v>
       </c>
       <c r="F25" t="n">
         <v>10.05992016213009</v>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0770444701067762</v>
+        <v>0.07703998663367427</v>
       </c>
       <c r="F26" t="n">
         <v>0.8440441282866774</v>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.0798556336199544</v>
+        <v>0.07991480881440588</v>
       </c>
       <c r="F27" t="n">
         <v>0.8440441282866774</v>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.08684020611782156</v>
+        <v>0.08684986004839781</v>
       </c>
       <c r="F28" t="n">
         <v>1.254614652958397</v>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.08913081885071661</v>
+        <v>0.08915633412009481</v>
       </c>
       <c r="F29" t="n">
         <v>1.254614652958397</v>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.04299957001156194</v>
+        <v>0.04300757720150106</v>
       </c>
       <c r="F30" t="n">
         <v>4.481984426888731</v>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.03828644894044857</v>
+        <v>0.03834305175536314</v>
       </c>
       <c r="F31" t="n">
         <v>4.481984426888731</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.05357661644129837</v>
+        <v>0.05350373017714808</v>
       </c>
       <c r="F32" t="n">
         <v>1.621707514273231</v>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.04954374718834017</v>
+        <v>0.04944062056316121</v>
       </c>
       <c r="F33" t="n">
         <v>1.621707514273231</v>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.01725923912857561</v>
+        <v>0.01725270808322658</v>
       </c>
       <c r="F34" t="n">
         <v>11.8803921636882</v>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.01720664281228325</v>
+        <v>0.01721092893612854</v>
       </c>
       <c r="F35" t="n">
         <v>11.8803921636882</v>
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.004435682978614336</v>
+        <v>0.004432150174933367</v>
       </c>
       <c r="F36" t="n">
         <v>40.81661019133534</v>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.003872037725200829</v>
+        <v>0.003875334392401145</v>
       </c>
       <c r="F37" t="n">
         <v>40.81661019133534</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.01125991267282692</v>
+        <v>0.01126323301726223</v>
       </c>
       <c r="F38" t="n">
         <v>19.05817478384657</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.01113993651518115</v>
+        <v>0.01115177485694947</v>
       </c>
       <c r="F39" t="n">
         <v>19.05817478384657</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.005871768785726388</v>
+        <v>0.005870279177476241</v>
       </c>
       <c r="F40" t="n">
         <v>33.25889734469793</v>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.005534126154013999</v>
+        <v>0.005543984377828929</v>
       </c>
       <c r="F41" t="n">
         <v>33.25889734469793</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.01080132715003012</v>
+        <v>0.01079201064516148</v>
       </c>
       <c r="F42" t="n">
         <v>16.38970637248534</v>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.01038178187842541</v>
+        <v>0.01038324434214667</v>
       </c>
       <c r="F43" t="n">
         <v>16.38970637248534</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.005508995957743399</v>
+        <v>0.005516567721417359</v>
       </c>
       <c r="F44" t="n">
         <v>30.52335899097242</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.004979368140238442</v>
+        <v>0.004987857458329205</v>
       </c>
       <c r="F45" t="n">
         <v>30.52335899097242</v>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.008698390158425983</v>
+        <v>0.008704381015335352</v>
       </c>
       <c r="F46" t="n">
         <v>24.19350636189434</v>
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.008504278206163458</v>
+        <v>0.008513493797854226</v>
       </c>
       <c r="F47" t="n">
         <v>24.19350636189434</v>
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.005148225617801435</v>
+        <v>0.005149932702562838</v>
       </c>
       <c r="F48" t="n">
         <v>42.70877068563502</v>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.005018568581003537</v>
+        <v>0.005021341062313957</v>
       </c>
       <c r="F49" t="n">
         <v>42.70877068563502</v>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.007343343599509968</v>
+        <v>0.007346313305882534</v>
       </c>
       <c r="F50" t="n">
         <v>22.02734034403161</v>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.00673002588683575</v>
+        <v>0.006745768096641967</v>
       </c>
       <c r="F51" t="n">
         <v>22.02734034403161</v>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.01520709371837004</v>
+        <v>0.01519644147682165</v>
       </c>
       <c r="F52" t="n">
         <v>14.68264699299626</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.01498721679063774</v>
+        <v>0.01499446374453352</v>
       </c>
       <c r="F53" t="n">
         <v>14.68264699299626</v>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.008036686855735884</v>
+        <v>0.008031839703599363</v>
       </c>
       <c r="F54" t="n">
         <v>26.1281172770193</v>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.007997599897376024</v>
+        <v>0.008005732921652672</v>
       </c>
       <c r="F55" t="n">
         <v>26.1281172770193</v>
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.008351958742441797</v>
+        <v>0.008363043171233493</v>
       </c>
       <c r="F56" t="n">
         <v>24.43832250664904</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.008028758658420079</v>
+        <v>0.008055590526166213</v>
       </c>
       <c r="F57" t="n">
         <v>24.43832250664904</v>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.008991707586112736</v>
+        <v>0.008986422166872808</v>
       </c>
       <c r="F58" t="n">
         <v>25.14257025564731</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.008521740272650178</v>
+        <v>0.00852464934115525</v>
       </c>
       <c r="F59" t="n">
         <v>25.14257025564731</v>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.003425569414689234</v>
+        <v>0.003419944237368598</v>
       </c>
       <c r="F60" t="n">
         <v>64.87424396895483</v>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.003032553614809488</v>
+        <v>0.003032599388919258</v>
       </c>
       <c r="F61" t="n">
         <v>64.87424396895483</v>
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.00389593781914585</v>
+        <v>0.003895660806877813</v>
       </c>
       <c r="F62" t="n">
         <v>48.24737092155696</v>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.003423179735445172</v>
+        <v>0.003429153231106134</v>
       </c>
       <c r="F63" t="n">
         <v>48.24737092155696</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.004121678123284167</v>
+        <v>0.004117548081561346</v>
       </c>
       <c r="F64" t="n">
         <v>42.07107102770869</v>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.003655953037607932</v>
+        <v>0.003658342504612569</v>
       </c>
       <c r="F65" t="n">
         <v>42.07107102770869</v>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.00439867516966085</v>
+        <v>0.004393728337269414</v>
       </c>
       <c r="F66" t="n">
         <v>40.32418949488441</v>
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.003996681194686089</v>
+        <v>0.003998756938983127</v>
       </c>
       <c r="F67" t="n">
         <v>40.32418949488441</v>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.008354986995111812</v>
+        <v>0.008354415403290323</v>
       </c>
       <c r="F68" t="n">
         <v>21.79457757467633</v>
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.00780525464998337</v>
+        <v>0.007821812683234473</v>
       </c>
       <c r="F69" t="n">
         <v>21.79457757467633</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.00518700693833379</v>
+        <v>0.005188314960888067</v>
       </c>
       <c r="F70" t="n">
         <v>35.27900051644691</v>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.00461459807927354</v>
+        <v>0.004625561579605862</v>
       </c>
       <c r="F71" t="n">
         <v>35.27900051644691</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.011801211923145</v>
+        <v>0.01179132028489065</v>
       </c>
       <c r="F72" t="n">
         <v>15.48239598695274</v>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.01180099097500488</v>
+        <v>0.01179715405740357</v>
       </c>
       <c r="F73" t="n">
         <v>15.48239598695274</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.006092536983720948</v>
+        <v>0.006090232884203624</v>
       </c>
       <c r="F74" t="n">
         <v>26.01227642789845</v>
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.005278172664507736</v>
+        <v>0.005281032523539481</v>
       </c>
       <c r="F75" t="n">
         <v>26.01227642789845</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.006287306016901726</v>
+        <v>0.006287656452529144</v>
       </c>
       <c r="F76" t="n">
         <v>24.55723338600139</v>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.005550914315648226</v>
+        <v>0.005556563519296929</v>
       </c>
       <c r="F77" t="n">
         <v>24.55723338600139</v>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.008290858430706174</v>
+        <v>0.008293003791240532</v>
       </c>
       <c r="F78" t="n">
         <v>23.555089386247</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.007740864334062557</v>
+        <v>0.007752527675802487</v>
       </c>
       <c r="F79" t="n">
         <v>23.555089386247</v>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.005571812817541918</v>
+        <v>0.005571001954909468</v>
       </c>
       <c r="F80" t="n">
         <v>30.94992821931555</v>
@@ -3900,7 +3900,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.00494288023470335</v>
+        <v>0.004950935366560855</v>
       </c>
       <c r="F81" t="n">
         <v>30.94992821931555</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.00973370295903799</v>
+        <v>0.009735754338706755</v>
       </c>
       <c r="F82" t="n">
         <v>17.11041974211544</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.009024338566598983</v>
+        <v>0.009028623535578208</v>
       </c>
       <c r="F83" t="n">
         <v>17.11041974211544</v>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.006404969273685094</v>
+        <v>0.006402123463315978</v>
       </c>
       <c r="F84" t="n">
         <v>25.09099671696914</v>
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.005694308826192416</v>
+        <v>0.0057077128143095</v>
       </c>
       <c r="F85" t="n">
         <v>25.09099671696914</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.003659032971349326</v>
+        <v>0.003660748281268807</v>
       </c>
       <c r="F86" t="n">
         <v>56.10647072185828</v>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.003120846251173886</v>
+        <v>0.003127264947772674</v>
       </c>
       <c r="F87" t="n">
         <v>56.10647072185828</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.007253177099578916</v>
+        <v>0.007256670623304129</v>
       </c>
       <c r="F88" t="n">
         <v>26.61131083407046</v>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.00687518567847701</v>
+        <v>0.006889884636057469</v>
       </c>
       <c r="F89" t="n">
         <v>26.61131083407046</v>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.0104904364263827</v>
+        <v>0.01050929668201439</v>
       </c>
       <c r="F90" t="n">
         <v>17.17910082644781</v>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.009609797190000886</v>
+        <v>0.009635573288869865</v>
       </c>
       <c r="F91" t="n">
         <v>17.17910082644781</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.004344154840230101</v>
+        <v>0.004348070291921096</v>
       </c>
       <c r="F92" t="n">
         <v>41.33077231855378</v>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.003821531239041694</v>
+        <v>0.003825029196864539</v>
       </c>
       <c r="F93" t="n">
         <v>41.33077231855378</v>
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.005293746764075413</v>
+        <v>0.005286167385222518</v>
       </c>
       <c r="F94" t="n">
         <v>31.93359446629537</v>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.004813585362009911</v>
+        <v>0.004811383006359608</v>
       </c>
       <c r="F95" t="n">
         <v>31.93359446629537</v>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.00556548240487467</v>
+        <v>0.00556676629894845</v>
       </c>
       <c r="F96" t="n">
         <v>35.1035288170361</v>
@@ -4588,7 +4588,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.004978947409649609</v>
+        <v>0.004985083110206851</v>
       </c>
       <c r="F97" t="n">
         <v>35.1035288170361</v>
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.002821445252509954</v>
+        <v>0.002819116863285473</v>
       </c>
       <c r="F98" t="n">
         <v>70.42713629849885</v>
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.002407556506557047</v>
+        <v>0.002412031454073541</v>
       </c>
       <c r="F99" t="n">
         <v>70.42713629849885</v>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.003833338430956611</v>
+        <v>0.003838233169937237</v>
       </c>
       <c r="F100" t="n">
         <v>48.09727907943265</v>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.003333497173893375</v>
+        <v>0.003344102866500507</v>
       </c>
       <c r="F101" t="n">
         <v>48.09727907943265</v>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.003871531934708696</v>
+        <v>0.003865176224263662</v>
       </c>
       <c r="F102" t="n">
         <v>48.35560222806118</v>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.003406416482999087</v>
+        <v>0.003404776425320414</v>
       </c>
       <c r="F103" t="n">
         <v>48.35560222806118</v>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.004927144615654184</v>
+        <v>0.00493560187928254</v>
       </c>
       <c r="F104" t="n">
         <v>41.34715232351992</v>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.004302163323395535</v>
+        <v>0.004313711756344157</v>
       </c>
       <c r="F105" t="n">
         <v>41.34715232351992</v>
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.00379671158946894</v>
+        <v>0.003795786292231806</v>
       </c>
       <c r="F106" t="n">
         <v>48.82276869525922</v>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.00329031245825524</v>
+        <v>0.003297980258197792</v>
       </c>
       <c r="F107" t="n">
         <v>48.82276869525922</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.00537169596802977</v>
+        <v>0.005369574632961136</v>
       </c>
       <c r="F108" t="n">
         <v>34.72295925128499</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.004707701801209827</v>
+        <v>0.004708803342543386</v>
       </c>
       <c r="F109" t="n">
         <v>34.72295925128499</v>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.004835598049244562</v>
+        <v>0.004839066608541187</v>
       </c>
       <c r="F110" t="n">
         <v>43.26334017048392</v>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.004237844999792155</v>
+        <v>0.004247779057691589</v>
       </c>
       <c r="F111" t="n">
         <v>43.26334017048392</v>
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.002294164649458382</v>
+        <v>0.002291086125187665</v>
       </c>
       <c r="F112" t="n">
         <v>91.05438059951148</v>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.0019838942655688</v>
+        <v>0.001986214162255315</v>
       </c>
       <c r="F113" t="n">
         <v>91.05438059951148</v>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.006188012207992152</v>
+        <v>0.006187853320152128</v>
       </c>
       <c r="F114" t="n">
         <v>29.15344518718943</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.00544517591465642</v>
+        <v>0.005452078685300045</v>
       </c>
       <c r="F115" t="n">
         <v>29.15344518718943</v>
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.004062998745426367</v>
+        <v>0.004062080883863377</v>
       </c>
       <c r="F116" t="n">
         <v>49.72373786348046</v>
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.003488196074873609</v>
+        <v>0.003492975728036105</v>
       </c>
       <c r="F117" t="n">
         <v>49.72373786348046</v>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.01059054194756658</v>
+        <v>0.01060345902469011</v>
       </c>
       <c r="F118" t="n">
         <v>19.85800760568668</v>
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.009824553452585731</v>
+        <v>0.00985230037944234</v>
       </c>
       <c r="F119" t="n">
         <v>19.85800760568668</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.004213994893926232</v>
+        <v>0.004210226863312507</v>
       </c>
       <c r="F120" t="n">
         <v>44.79676977747089</v>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.00374882727311947</v>
+        <v>0.003745658852760906</v>
       </c>
       <c r="F121" t="n">
         <v>44.79676977747089</v>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.002420796126654687</v>
+        <v>0.002422078418753026</v>
       </c>
       <c r="F122" t="n">
         <v>86.85132295553052</v>
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.002060359281539855</v>
+        <v>0.002068228847933313</v>
       </c>
       <c r="F123" t="n">
         <v>86.85132295553052</v>
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.04179033937386568</v>
+        <v>0.04174556813317439</v>
       </c>
       <c r="F124" t="n">
         <v>5.437958953595492</v>
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.039043912858595</v>
+        <v>0.03902665104468529</v>
       </c>
       <c r="F125" t="n">
         <v>5.437958953595492</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.003954751683717904</v>
+        <v>0.003960010844178838</v>
       </c>
       <c r="F126" t="n">
         <v>47.57406740201719</v>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.003357803541787616</v>
+        <v>0.003369733595860298</v>
       </c>
       <c r="F127" t="n">
         <v>47.57406740201719</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.01863704493467331</v>
+        <v>0.01860949333090016</v>
       </c>
       <c r="F128" t="n">
         <v>11.3439055252793</v>
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.01768451489016436</v>
+        <v>0.01767924831933909</v>
       </c>
       <c r="F129" t="n">
         <v>11.3439055252793</v>

--- a/results/soae_T_xi [int 100ms, bw=10p max, kaiser, df=50hz, rip=100db, crop=200hz, tau=500ms, hop_psd=250ms, nfft=None, win=hann].xlsx
+++ b/results/soae_T_xi [int 100ms, bw=10p max, kaiser, df=50hz, rip=100db, crop=200hz, tau=500ms, hop_psd=250ms, nfft=None, win=hann].xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -585,7 +585,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -757,7 +757,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -843,7 +843,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E128" t="n">
